--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/94.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/94.xlsx
@@ -426,13 +426,13 @@
         <v>-4.53961178257728</v>
       </c>
       <c r="E2">
-        <v>-4.997242071434393</v>
+        <v>-5.800045360889777</v>
       </c>
       <c r="F2">
-        <v>0.57405266432073</v>
+        <v>-0.1639415115681551</v>
       </c>
       <c r="G2">
-        <v>-10.9222400371085</v>
+        <v>-11.60567292393636</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.488513664287186</v>
       </c>
       <c r="E3">
-        <v>-5.922012717866016</v>
+        <v>-6.569585580844607</v>
       </c>
       <c r="F3">
-        <v>1.032487752378032</v>
+        <v>-0.02210513139121256</v>
       </c>
       <c r="G3">
-        <v>-11.4379704397539</v>
+        <v>-11.17889711637167</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.356394358793976</v>
       </c>
       <c r="E4">
-        <v>-6.280069372602134</v>
+        <v>-7.754783343399604</v>
       </c>
       <c r="F4">
-        <v>1.192238406007917</v>
+        <v>0.09267345594068693</v>
       </c>
       <c r="G4">
-        <v>-10.89611431598523</v>
+        <v>-10.69644587502918</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.146848455578779</v>
       </c>
       <c r="E5">
-        <v>-7.002117621057551</v>
+        <v>-8.087480489786319</v>
       </c>
       <c r="F5">
-        <v>1.429776072230287</v>
+        <v>-0.06582470617616487</v>
       </c>
       <c r="G5">
-        <v>-10.28073309766932</v>
+        <v>-10.28793614199621</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.862554962247496</v>
       </c>
       <c r="E6">
-        <v>-8.170445039211094</v>
+        <v>-8.759573912426697</v>
       </c>
       <c r="F6">
-        <v>1.493311852025009</v>
+        <v>0.3794144891545414</v>
       </c>
       <c r="G6">
-        <v>-9.771110531994829</v>
+        <v>-9.929497879476195</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.509008363625441</v>
       </c>
       <c r="E7">
-        <v>-8.252570639948253</v>
+        <v>-10.27109779519612</v>
       </c>
       <c r="F7">
-        <v>1.187929238778554</v>
+        <v>0.4916789814189444</v>
       </c>
       <c r="G7">
-        <v>-9.039598172777024</v>
+        <v>-9.741854528106813</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.096372938964531</v>
       </c>
       <c r="E8">
-        <v>-9.659487589079221</v>
+        <v>-10.75787077531133</v>
       </c>
       <c r="F8">
-        <v>1.535634799368841</v>
+        <v>0.6748103049928451</v>
       </c>
       <c r="G8">
-        <v>-8.941097390098912</v>
+        <v>-9.29558559605257</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.63707797602664</v>
       </c>
       <c r="E9">
-        <v>-10.39214729246958</v>
+        <v>-11.81299411238402</v>
       </c>
       <c r="F9">
-        <v>1.426530528746118</v>
+        <v>0.720882443201748</v>
       </c>
       <c r="G9">
-        <v>-8.506146035847143</v>
+        <v>-8.248562142254132</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.145093161314823</v>
       </c>
       <c r="E10">
-        <v>-10.68201237046333</v>
+        <v>-12.61243745387761</v>
       </c>
       <c r="F10">
-        <v>1.836938531523911</v>
+        <v>0.975320461176033</v>
       </c>
       <c r="G10">
-        <v>-8.824472818469291</v>
+        <v>-7.748647630341692</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.642323209755386</v>
       </c>
       <c r="E11">
-        <v>-12.67130922440706</v>
+        <v>-13.22234899656266</v>
       </c>
       <c r="F11">
-        <v>1.756721088971612</v>
+        <v>1.208419734854203</v>
       </c>
       <c r="G11">
-        <v>-7.753352192094878</v>
+        <v>-7.568452733290758</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.150033037182119</v>
       </c>
       <c r="E12">
-        <v>-13.14234153360116</v>
+        <v>-14.32366434999009</v>
       </c>
       <c r="F12">
-        <v>1.947888404720071</v>
+        <v>0.9174573413556819</v>
       </c>
       <c r="G12">
-        <v>-6.856748093285729</v>
+        <v>-6.763077188101176</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.6856976590737122</v>
       </c>
       <c r="E13">
-        <v>-13.73770022380401</v>
+        <v>-14.84576039242296</v>
       </c>
       <c r="F13">
-        <v>2.265509317975485</v>
+        <v>1.496320482431976</v>
       </c>
       <c r="G13">
-        <v>-6.142354386351854</v>
+        <v>-6.237466422550701</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.2672959711590041</v>
       </c>
       <c r="E14">
-        <v>-15.55333469941135</v>
+        <v>-15.62889822625528</v>
       </c>
       <c r="F14">
-        <v>2.389457932456375</v>
+        <v>1.438076313606337</v>
       </c>
       <c r="G14">
-        <v>-5.445476164879758</v>
+        <v>-5.536194317931762</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.09527740431748084</v>
       </c>
       <c r="E15">
-        <v>-15.88981126810366</v>
+        <v>-16.27421589548449</v>
       </c>
       <c r="F15">
-        <v>2.292389840196329</v>
+        <v>1.447115458705686</v>
       </c>
       <c r="G15">
-        <v>-5.307096258572389</v>
+        <v>-5.201972016866621</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.4006471378235417</v>
       </c>
       <c r="E16">
-        <v>-17.06571829692502</v>
+        <v>-17.7123525341442</v>
       </c>
       <c r="F16">
-        <v>2.667941799399125</v>
+        <v>1.692350314834868</v>
       </c>
       <c r="G16">
-        <v>-4.723840252450135</v>
+        <v>-4.733481732225115</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.6495571510344166</v>
       </c>
       <c r="E17">
-        <v>-17.36575874266461</v>
+        <v>-18.14125882087056</v>
       </c>
       <c r="F17">
-        <v>2.695968782105443</v>
+        <v>2.143762504051236</v>
       </c>
       <c r="G17">
-        <v>-4.641549582938244</v>
+        <v>-3.549467288241783</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.849587510814195</v>
       </c>
       <c r="E18">
-        <v>-18.02654297086748</v>
+        <v>-18.67235071903302</v>
       </c>
       <c r="F18">
-        <v>2.795555111269999</v>
+        <v>2.300416720329456</v>
       </c>
       <c r="G18">
-        <v>-4.116959618522896</v>
+        <v>-3.536930492715257</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.01140445109622</v>
       </c>
       <c r="E19">
-        <v>-19.25445651189833</v>
+        <v>-18.95473586343076</v>
       </c>
       <c r="F19">
-        <v>3.339694747555744</v>
+        <v>2.382194807068629</v>
       </c>
       <c r="G19">
-        <v>-3.062409388068279</v>
+        <v>-2.941777323491299</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.142670698071075</v>
       </c>
       <c r="E20">
-        <v>-19.00729059953514</v>
+        <v>-20.08929767351344</v>
       </c>
       <c r="F20">
-        <v>3.700241659624229</v>
+        <v>2.563869032381006</v>
       </c>
       <c r="G20">
-        <v>-3.045264628338439</v>
+        <v>-3.063464128883089</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.249600011707934</v>
       </c>
       <c r="E21">
-        <v>-20.16316253692552</v>
+        <v>-21.27019686234724</v>
       </c>
       <c r="F21">
-        <v>3.701041862535333</v>
+        <v>2.822442260430066</v>
       </c>
       <c r="G21">
-        <v>-3.463816590441129</v>
+        <v>-2.4714046919996</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.333968663603575</v>
       </c>
       <c r="E22">
-        <v>-19.21581918694345</v>
+        <v>-21.09483997379033</v>
       </c>
       <c r="F22">
-        <v>3.993813410441568</v>
+        <v>2.953887599906291</v>
       </c>
       <c r="G22">
-        <v>-3.020838501943983</v>
+        <v>-2.247765699580246</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.391849725077825</v>
       </c>
       <c r="E23">
-        <v>-22.09698910041483</v>
+        <v>-22.19648343091243</v>
       </c>
       <c r="F23">
-        <v>4.264749193610008</v>
+        <v>3.311084594197855</v>
       </c>
       <c r="G23">
-        <v>-3.171522847509268</v>
+        <v>-2.290440930666583</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.417589210305399</v>
       </c>
       <c r="E24">
-        <v>-21.79791219970261</v>
+        <v>-22.03830007118368</v>
       </c>
       <c r="F24">
-        <v>4.505298803708957</v>
+        <v>3.372595844060135</v>
       </c>
       <c r="G24">
-        <v>-2.167981344875823</v>
+        <v>-1.899889204303582</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.404972741788363</v>
       </c>
       <c r="E25">
-        <v>-21.94796357165734</v>
+        <v>-23.25954355482687</v>
       </c>
       <c r="F25">
-        <v>4.391270717243994</v>
+        <v>3.553272715019541</v>
       </c>
       <c r="G25">
-        <v>-2.241322381929378</v>
+        <v>-2.646131384504448</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.349130777854223</v>
       </c>
       <c r="E26">
-        <v>-21.11286906415141</v>
+        <v>-22.6047316445091</v>
       </c>
       <c r="F26">
-        <v>4.440376336881948</v>
+        <v>3.810136192749223</v>
       </c>
       <c r="G26">
-        <v>-2.641418990517489</v>
+        <v>-2.525794334066263</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.249179169743917</v>
       </c>
       <c r="E27">
-        <v>-21.39415360754808</v>
+        <v>-22.75914804156622</v>
       </c>
       <c r="F27">
-        <v>4.297509467655923</v>
+        <v>4.002575880828381</v>
       </c>
       <c r="G27">
-        <v>-3.011142196532588</v>
+        <v>-2.569025653750508</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.110287836682158</v>
       </c>
       <c r="E28">
-        <v>-22.0100997662881</v>
+        <v>-22.41426537315246</v>
       </c>
       <c r="F28">
-        <v>4.6844481651776</v>
+        <v>4.016861905057062</v>
       </c>
       <c r="G28">
-        <v>-2.773386908109083</v>
+        <v>-2.542184588609273</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.9419775049196143</v>
       </c>
       <c r="E29">
-        <v>-21.56921561810092</v>
+        <v>-22.44790223167225</v>
       </c>
       <c r="F29">
-        <v>4.894271971571909</v>
+        <v>3.631621360711124</v>
       </c>
       <c r="G29">
-        <v>-2.783965645192274</v>
+        <v>-2.849106333485142</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.7539177708788722</v>
       </c>
       <c r="E30">
-        <v>-21.65360056579879</v>
+        <v>-22.69305798975423</v>
       </c>
       <c r="F30">
-        <v>4.289631693655299</v>
+        <v>3.994322028026887</v>
       </c>
       <c r="G30">
-        <v>-3.149924157506988</v>
+        <v>-3.250709341702325</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.5552013950098422</v>
       </c>
       <c r="E31">
-        <v>-20.72095543069529</v>
+        <v>-22.11799189008449</v>
       </c>
       <c r="F31">
-        <v>5.0049054084202</v>
+        <v>4.074358886485375</v>
       </c>
       <c r="G31">
-        <v>-3.167859972847936</v>
+        <v>-3.433430134145162</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.3553406554746786</v>
       </c>
       <c r="E32">
-        <v>-21.44794184741593</v>
+        <v>-21.82055550784557</v>
       </c>
       <c r="F32">
-        <v>4.491108870099001</v>
+        <v>4.143434787470021</v>
       </c>
       <c r="G32">
-        <v>-3.916000164366542</v>
+        <v>-3.772933971518125</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.1640652849906695</v>
       </c>
       <c r="E33">
-        <v>-20.42478162469912</v>
+        <v>-21.59822579920485</v>
       </c>
       <c r="F33">
-        <v>4.689517773682733</v>
+        <v>4.169155595326945</v>
       </c>
       <c r="G33">
-        <v>-3.692491709176742</v>
+        <v>-4.132316018207824</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.007922039231351435</v>
       </c>
       <c r="E34">
-        <v>-20.07991556913066</v>
+        <v>-21.46207937876565</v>
       </c>
       <c r="F34">
-        <v>4.796539528654818</v>
+        <v>3.970090624760196</v>
       </c>
       <c r="G34">
-        <v>-4.309956301676354</v>
+        <v>-4.04936221956979</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.1471465506457151</v>
       </c>
       <c r="E35">
-        <v>-19.62371437757751</v>
+        <v>-20.31343818229179</v>
       </c>
       <c r="F35">
-        <v>4.087914290664786</v>
+        <v>3.931760408297857</v>
       </c>
       <c r="G35">
-        <v>-4.116398308435806</v>
+        <v>-4.528230213960971</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.2403060447558224</v>
       </c>
       <c r="E36">
-        <v>-19.54303824759272</v>
+        <v>-19.3133158227938</v>
       </c>
       <c r="F36">
-        <v>4.545665147247377</v>
+        <v>4.033485582096442</v>
       </c>
       <c r="G36">
-        <v>-4.121512757089797</v>
+        <v>-4.749584804863103</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.277799720904659</v>
       </c>
       <c r="E37">
-        <v>-17.89163836061439</v>
+        <v>-19.33519078684168</v>
       </c>
       <c r="F37">
-        <v>4.496012805123574</v>
+        <v>4.03021518759019</v>
       </c>
       <c r="G37">
-        <v>-4.453946698110025</v>
+        <v>-4.649491467984411</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.2542835123058381</v>
       </c>
       <c r="E38">
-        <v>-17.96088485303326</v>
+        <v>-18.71919478956575</v>
       </c>
       <c r="F38">
-        <v>4.169359373708034</v>
+        <v>4.013079579495879</v>
       </c>
       <c r="G38">
-        <v>-4.721759489011017</v>
+        <v>-5.008090291296775</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.1739017828356347</v>
       </c>
       <c r="E39">
-        <v>-18.15694134683312</v>
+        <v>-18.3849858742568</v>
       </c>
       <c r="F39">
-        <v>5.098065263273838</v>
+        <v>3.930014209812756</v>
       </c>
       <c r="G39">
-        <v>-4.797290940776516</v>
+        <v>-5.066195022916593</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.04959460498849115</v>
       </c>
       <c r="E40">
-        <v>-17.12991448437289</v>
+        <v>-17.52952401841392</v>
       </c>
       <c r="F40">
-        <v>4.517747509038228</v>
+        <v>3.761885448270957</v>
       </c>
       <c r="G40">
-        <v>-5.025503957719502</v>
+        <v>-5.434738172376509</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.1022445407752196</v>
       </c>
       <c r="E41">
-        <v>-16.66306861219422</v>
+        <v>-16.8063710157461</v>
       </c>
       <c r="F41">
-        <v>4.341659793490331</v>
+        <v>4.079334061106589</v>
       </c>
       <c r="G41">
-        <v>-4.102514368700266</v>
+        <v>-5.762942707159134</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.2632242122450278</v>
       </c>
       <c r="E42">
-        <v>-15.95877949536377</v>
+        <v>-16.75393256955881</v>
       </c>
       <c r="F42">
-        <v>4.651389678866678</v>
+        <v>3.86532037238892</v>
       </c>
       <c r="G42">
-        <v>-4.871109744090244</v>
+        <v>-5.396365448376326</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.4145468022276505</v>
       </c>
       <c r="E43">
-        <v>-15.69988076100793</v>
+        <v>-15.2936634677491</v>
       </c>
       <c r="F43">
-        <v>4.802101187397214</v>
+        <v>3.754524575529681</v>
       </c>
       <c r="G43">
-        <v>-5.140606465252504</v>
+        <v>-5.885566769859134</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.5371985526337795</v>
       </c>
       <c r="E44">
-        <v>-14.86769765464071</v>
+        <v>-15.92235167883369</v>
       </c>
       <c r="F44">
-        <v>4.174980674903431</v>
+        <v>3.858842539299028</v>
       </c>
       <c r="G44">
-        <v>-5.093529518785549</v>
+        <v>-5.832769681993049</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.6155599270122153</v>
       </c>
       <c r="E45">
-        <v>-13.30637261487527</v>
+        <v>-14.39651167662759</v>
       </c>
       <c r="F45">
-        <v>4.600604130135845</v>
+        <v>3.576781781910991</v>
       </c>
       <c r="G45">
-        <v>-5.000310272415258</v>
+        <v>-5.643049483301438</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.641936580840954</v>
       </c>
       <c r="E46">
-        <v>-13.4030967534192</v>
+        <v>-14.53201019610012</v>
       </c>
       <c r="F46">
-        <v>4.676462703414613</v>
+        <v>3.541322686866755</v>
       </c>
       <c r="G46">
-        <v>-5.404385655760226</v>
+        <v>-6.023792642235626</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.6162526516866831</v>
       </c>
       <c r="E47">
-        <v>-13.85202567194256</v>
+        <v>-13.27495357120294</v>
       </c>
       <c r="F47">
-        <v>4.411603823513111</v>
+        <v>3.696596843051911</v>
       </c>
       <c r="G47">
-        <v>-5.08018861392496</v>
+        <v>-6.248606469720983</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.5446485707069803</v>
       </c>
       <c r="E48">
-        <v>-12.94300815606602</v>
+        <v>-12.35517923799508</v>
       </c>
       <c r="F48">
-        <v>4.532091518985104</v>
+        <v>3.463918380014364</v>
       </c>
       <c r="G48">
-        <v>-5.538423893812573</v>
+        <v>-6.412790975566915</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.437765959288252</v>
       </c>
       <c r="E49">
-        <v>-12.06247336345514</v>
+        <v>-11.86828996796278</v>
       </c>
       <c r="F49">
-        <v>4.141948696349398</v>
+        <v>3.681634871022546</v>
       </c>
       <c r="G49">
-        <v>-5.420099727454136</v>
+        <v>-6.350924160991303</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.3073441524128804</v>
       </c>
       <c r="E50">
-        <v>-11.9697113885151</v>
+        <v>-11.17363214819461</v>
       </c>
       <c r="F50">
-        <v>3.919780558918571</v>
+        <v>3.569419252434909</v>
       </c>
       <c r="G50">
-        <v>-5.270222101967505</v>
+        <v>-6.436674067086419</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.1644941264977187</v>
       </c>
       <c r="E51">
-        <v>-10.5101317197853</v>
+        <v>-10.69229987491493</v>
       </c>
       <c r="F51">
-        <v>4.132960910029023</v>
+        <v>3.522283490480811</v>
       </c>
       <c r="G51">
-        <v>-5.467570896354349</v>
+        <v>-6.31259843039376</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.01826214577235242</v>
       </c>
       <c r="E52">
-        <v>-10.14887709232907</v>
+        <v>-9.84845870435892</v>
       </c>
       <c r="F52">
-        <v>3.849755348890318</v>
+        <v>3.46154427903794</v>
       </c>
       <c r="G52">
-        <v>-5.168964373001177</v>
+        <v>-6.699978102078558</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1274678915384558</v>
       </c>
       <c r="E53">
-        <v>-10.350918363648</v>
+        <v>-9.038001046431878</v>
       </c>
       <c r="F53">
-        <v>3.747506646893163</v>
+        <v>3.116651854147561</v>
       </c>
       <c r="G53">
-        <v>-6.03550444247136</v>
+        <v>-6.577664717984901</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.2734615322520491</v>
       </c>
       <c r="E54">
-        <v>-10.20285637991786</v>
+        <v>-8.767606223128915</v>
       </c>
       <c r="F54">
-        <v>3.671754104641954</v>
+        <v>3.460932943894674</v>
       </c>
       <c r="G54">
-        <v>-5.776210511171171</v>
+        <v>-6.892538790885301</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.4225931472304587</v>
       </c>
       <c r="E55">
-        <v>-9.399305512424013</v>
+        <v>-8.727320073278079</v>
       </c>
       <c r="F55">
-        <v>3.961808607467006</v>
+        <v>3.245998110625092</v>
       </c>
       <c r="G55">
-        <v>-6.045908259666946</v>
+        <v>-7.123707170705427</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.5805776890326374</v>
       </c>
       <c r="E56">
-        <v>-9.29156290423531</v>
+        <v>-7.759966551132989</v>
       </c>
       <c r="F56">
-        <v>3.574841745453635</v>
+        <v>3.051326800762792</v>
       </c>
       <c r="G56">
-        <v>-5.638749586959874</v>
+        <v>-7.15933600214035</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.7545386855044354</v>
       </c>
       <c r="E57">
-        <v>-8.654177868636523</v>
+        <v>-7.248639785665398</v>
       </c>
       <c r="F57">
-        <v>4.00932210495678</v>
+        <v>2.993745325859392</v>
       </c>
       <c r="G57">
-        <v>-6.080813914850132</v>
+        <v>-7.032649620856578</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.9505178248929275</v>
       </c>
       <c r="E58">
-        <v>-8.209697039442048</v>
+        <v>-7.286932394080318</v>
       </c>
       <c r="F58">
-        <v>3.520545575669738</v>
+        <v>2.939825234876367</v>
       </c>
       <c r="G58">
-        <v>-6.513704086247216</v>
+        <v>-7.64181465630104</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.176786608344666</v>
       </c>
       <c r="E59">
-        <v>-7.812550359716644</v>
+        <v>-6.771145079649862</v>
       </c>
       <c r="F59">
-        <v>3.601294830094634</v>
+        <v>2.916321138189334</v>
       </c>
       <c r="G59">
-        <v>-6.490894010754659</v>
+        <v>-7.492654985576965</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.440293642713451</v>
       </c>
       <c r="E60">
-        <v>-7.243577021060433</v>
+        <v>-6.303211066104079</v>
       </c>
       <c r="F60">
-        <v>3.623685600992304</v>
+        <v>2.918411937514</v>
       </c>
       <c r="G60">
-        <v>-6.731348809085375</v>
+        <v>-7.69149582049763</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.742630839863307</v>
       </c>
       <c r="E61">
-        <v>-6.297616690449535</v>
+        <v>-5.752013471918135</v>
       </c>
       <c r="F61">
-        <v>3.375268157301566</v>
+        <v>2.720132259245104</v>
       </c>
       <c r="G61">
-        <v>-6.658924143383302</v>
+        <v>-8.164788569814489</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.0835745293501</v>
       </c>
       <c r="E62">
-        <v>-6.713141330287306</v>
+        <v>-5.438911176561961</v>
       </c>
       <c r="F62">
-        <v>3.406762685956004</v>
+        <v>2.864972299624598</v>
       </c>
       <c r="G62">
-        <v>-6.410143680551526</v>
+        <v>-8.061246439330937</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.457065193876125</v>
       </c>
       <c r="E63">
-        <v>-5.898127599536927</v>
+        <v>-5.060740519379697</v>
       </c>
       <c r="F63">
-        <v>3.787803407569748</v>
+        <v>2.740493530005916</v>
       </c>
       <c r="G63">
-        <v>-6.928402589333424</v>
+        <v>-8.089231010603079</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.850726933467397</v>
       </c>
       <c r="E64">
-        <v>-6.684048084956882</v>
+        <v>-5.013481127714473</v>
       </c>
       <c r="F64">
-        <v>3.247770816867083</v>
+        <v>2.417754962936006</v>
       </c>
       <c r="G64">
-        <v>-6.617251438219951</v>
+        <v>-8.005655854752362</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.253084926160229</v>
       </c>
       <c r="E65">
-        <v>-5.662997693593084</v>
+        <v>-3.802342407224598</v>
       </c>
       <c r="F65">
-        <v>3.782203643926823</v>
+        <v>2.547984259064922</v>
       </c>
       <c r="G65">
-        <v>-6.758675472720558</v>
+        <v>-8.297641529822471</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.649431531628884</v>
       </c>
       <c r="E66">
-        <v>-5.63488460613532</v>
+        <v>-5.258740716079573</v>
       </c>
       <c r="F66">
-        <v>3.485656397398628</v>
+        <v>2.746426297344766</v>
       </c>
       <c r="G66">
-        <v>-6.732304341605723</v>
+        <v>-8.212280624671431</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.021583157698662</v>
       </c>
       <c r="E67">
-        <v>-6.765438567289547</v>
+        <v>-4.355130681347952</v>
       </c>
       <c r="F67">
-        <v>3.551513262655995</v>
+        <v>2.256407216953524</v>
       </c>
       <c r="G67">
-        <v>-7.18072322183075</v>
+        <v>-7.981775373977448</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.354094132805034</v>
       </c>
       <c r="E68">
-        <v>-6.069298051078411</v>
+        <v>-4.526263753987513</v>
       </c>
       <c r="F68">
-        <v>3.136279191389492</v>
+        <v>2.463916564824412</v>
       </c>
       <c r="G68">
-        <v>-6.427659166013305</v>
+        <v>-7.961129605750925</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.630214043803557</v>
       </c>
       <c r="E69">
-        <v>-5.415997909682881</v>
+        <v>-4.368292208036334</v>
       </c>
       <c r="F69">
-        <v>3.158751142292637</v>
+        <v>2.420526680265774</v>
       </c>
       <c r="G69">
-        <v>-6.77744150484148</v>
+        <v>-7.971795802777917</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.834145064149812</v>
       </c>
       <c r="E70">
-        <v>-5.498891854515134</v>
+        <v>-4.141800981648134</v>
       </c>
       <c r="F70">
-        <v>3.350973798112262</v>
+        <v>2.12266895650635</v>
       </c>
       <c r="G70">
-        <v>-6.523765895901367</v>
+        <v>-7.843767498774313</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.957936250322705</v>
       </c>
       <c r="E71">
-        <v>-5.25228662568079</v>
+        <v>-4.394577882511173</v>
       </c>
       <c r="F71">
-        <v>3.538627179338046</v>
+        <v>2.257916502361425</v>
       </c>
       <c r="G71">
-        <v>-6.485108600740753</v>
+        <v>-7.90999556218938</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.997333860066308</v>
       </c>
       <c r="E72">
-        <v>-5.605695836944425</v>
+        <v>-4.432725128529724</v>
       </c>
       <c r="F72">
-        <v>3.321331498970485</v>
+        <v>2.187084462482845</v>
       </c>
       <c r="G72">
-        <v>-6.814229506874858</v>
+        <v>-7.597622582607266</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.952678552723192</v>
       </c>
       <c r="E73">
-        <v>-6.898208426921665</v>
+        <v>-5.037818946077969</v>
       </c>
       <c r="F73">
-        <v>2.881514796658504</v>
+        <v>2.325337325275277</v>
       </c>
       <c r="G73">
-        <v>-6.629284360040392</v>
+        <v>-7.442980348241853</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.83059070295932</v>
       </c>
       <c r="E74">
-        <v>-6.486284621302521</v>
+        <v>-5.2223793509307</v>
       </c>
       <c r="F74">
-        <v>2.920517647451916</v>
+        <v>2.208380131674015</v>
       </c>
       <c r="G74">
-        <v>-5.776385431058776</v>
+        <v>-7.400007492272128</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.638043242188565</v>
       </c>
       <c r="E75">
-        <v>-6.577547286954304</v>
+        <v>-5.435239737750812</v>
       </c>
       <c r="F75">
-        <v>2.827781916708511</v>
+        <v>2.130561641120223</v>
       </c>
       <c r="G75">
-        <v>-6.470154255722855</v>
+        <v>-7.089255785081096</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.38431223980816</v>
       </c>
       <c r="E76">
-        <v>-6.611412572096955</v>
+        <v>-5.758525707275465</v>
       </c>
       <c r="F76">
-        <v>2.866087282148766</v>
+        <v>2.234743752635512</v>
       </c>
       <c r="G76">
-        <v>-5.812520746944375</v>
+        <v>-7.308989103592146</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.082439501147303</v>
       </c>
       <c r="E77">
-        <v>-8.104703857150383</v>
+        <v>-6.401019192803791</v>
       </c>
       <c r="F77">
-        <v>3.130059808929273</v>
+        <v>1.957139611874536</v>
       </c>
       <c r="G77">
-        <v>-4.921920055322491</v>
+        <v>-6.331012011994882</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.743407889649562</v>
       </c>
       <c r="E78">
-        <v>-8.083912881258291</v>
+        <v>-7.492096880315523</v>
       </c>
       <c r="F78">
-        <v>2.875172815822671</v>
+        <v>2.214122374510221</v>
       </c>
       <c r="G78">
-        <v>-5.025208943580705</v>
+        <v>-6.646857281883176</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.379129916714938</v>
       </c>
       <c r="E79">
-        <v>-7.69926736762062</v>
+        <v>-7.676744502606075</v>
       </c>
       <c r="F79">
-        <v>2.621833213024498</v>
+        <v>2.220257263495354</v>
       </c>
       <c r="G79">
-        <v>-5.032153524193067</v>
+        <v>-5.863205742436248</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.002119783435798</v>
       </c>
       <c r="E80">
-        <v>-9.283405997193347</v>
+        <v>-7.755240196645334</v>
       </c>
       <c r="F80">
-        <v>2.947896846849245</v>
+        <v>2.129171640618326</v>
       </c>
       <c r="G80">
-        <v>-4.939038707606421</v>
+        <v>-5.550341942871005</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.620143868942077</v>
       </c>
       <c r="E81">
-        <v>-10.61426518733273</v>
+        <v>-9.336974116860985</v>
       </c>
       <c r="F81">
-        <v>2.742070741540847</v>
+        <v>2.182848191584928</v>
       </c>
       <c r="G81">
-        <v>-4.739671807650645</v>
+        <v>-5.641383828252308</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.240765784221584</v>
       </c>
       <c r="E82">
-        <v>-11.21150943547705</v>
+        <v>-9.991819252869352</v>
       </c>
       <c r="F82">
-        <v>2.81430934926938</v>
+        <v>2.373952551410774</v>
       </c>
       <c r="G82">
-        <v>-4.365779242523538</v>
+        <v>-5.114720932631616</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.870554515267276</v>
       </c>
       <c r="E83">
-        <v>-11.25049147697189</v>
+        <v>-11.29671256580591</v>
       </c>
       <c r="F83">
-        <v>2.453952961703539</v>
+        <v>2.353735416578049</v>
       </c>
       <c r="G83">
-        <v>-4.173111513188561</v>
+        <v>-4.504723069662587</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.511723707139339</v>
       </c>
       <c r="E84">
-        <v>-12.7194740161411</v>
+        <v>-12.20010248033731</v>
       </c>
       <c r="F84">
-        <v>2.885040328324819</v>
+        <v>2.278773136829111</v>
       </c>
       <c r="G84">
-        <v>-4.038055084745679</v>
+        <v>-4.535571627751182</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.16873200885694</v>
       </c>
       <c r="E85">
-        <v>-13.6410799155432</v>
+        <v>-13.50387442621616</v>
       </c>
       <c r="F85">
-        <v>3.05919132088497</v>
+        <v>2.416197632218744</v>
       </c>
       <c r="G85">
-        <v>-3.84149212448076</v>
+        <v>-4.130992370700129</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.8490196955130195</v>
       </c>
       <c r="E86">
-        <v>-15.17656782765688</v>
+        <v>-14.99290451645031</v>
       </c>
       <c r="F86">
-        <v>2.540966330428405</v>
+        <v>2.348533269288469</v>
       </c>
       <c r="G86">
-        <v>-3.64495266091716</v>
+        <v>-4.106156357404869</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.5598162150990339</v>
       </c>
       <c r="E87">
-        <v>-16.43117821108374</v>
+        <v>-16.1948272610104</v>
       </c>
       <c r="F87">
-        <v>3.009842161230592</v>
+        <v>2.306364398281557</v>
       </c>
       <c r="G87">
-        <v>-3.227773950469395</v>
+        <v>-3.496550106124508</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.3117818643873082</v>
       </c>
       <c r="E88">
-        <v>-18.24086113486261</v>
+        <v>-17.6511466588502</v>
       </c>
       <c r="F88">
-        <v>2.375287879664087</v>
+        <v>2.311783577830671</v>
       </c>
       <c r="G88">
-        <v>-2.630743655884427</v>
+        <v>-3.415217579877555</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.1180137327469223</v>
       </c>
       <c r="E89">
-        <v>-18.50486831914798</v>
+        <v>-19.04474010605112</v>
       </c>
       <c r="F89">
-        <v>2.652486120397691</v>
+        <v>2.38135152905258</v>
       </c>
       <c r="G89">
-        <v>-2.094849167389558</v>
+        <v>-2.849495334429218</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.01103780517210839</v>
       </c>
       <c r="E90">
-        <v>-20.98678172154094</v>
+        <v>-20.35923564357067</v>
       </c>
       <c r="F90">
-        <v>2.849799922274922</v>
+        <v>2.517911208873689</v>
       </c>
       <c r="G90">
-        <v>-2.099817414346447</v>
+        <v>-2.908383289426369</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.06623329143636054</v>
       </c>
       <c r="E91">
-        <v>-22.62604177181679</v>
+        <v>-22.24707369806016</v>
       </c>
       <c r="F91">
-        <v>2.690329256827184</v>
+        <v>2.589379434917619</v>
       </c>
       <c r="G91">
-        <v>-2.179907226168029</v>
+        <v>-2.855685409854747</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.0395867928935487</v>
       </c>
       <c r="E92">
-        <v>-24.64202716173387</v>
+        <v>-24.07432470574305</v>
       </c>
       <c r="F92">
-        <v>2.514504962113377</v>
+        <v>2.567671238759855</v>
       </c>
       <c r="G92">
-        <v>-1.90410555681823</v>
+        <v>-2.627720413647917</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.07058729952365225</v>
       </c>
       <c r="E93">
-        <v>-26.55838531839095</v>
+        <v>-26.24813212600361</v>
       </c>
       <c r="F93">
-        <v>2.47903924012992</v>
+        <v>2.337187949339727</v>
       </c>
       <c r="G93">
-        <v>-2.897721008516262</v>
+        <v>-2.448012420463225</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.2616062354597199</v>
       </c>
       <c r="E94">
-        <v>-29.19239970252745</v>
+        <v>-28.87480155591215</v>
       </c>
       <c r="F94">
-        <v>2.680561148413372</v>
+        <v>2.614319920681107</v>
       </c>
       <c r="G94">
-        <v>-2.405924606909888</v>
+        <v>-2.531785992902869</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.5263799988389328</v>
       </c>
       <c r="E95">
-        <v>-31.31963093438572</v>
+        <v>-31.14083103364052</v>
       </c>
       <c r="F95">
-        <v>2.364800748344645</v>
+        <v>2.823365061716784</v>
       </c>
       <c r="G95">
-        <v>-2.606398462572295</v>
+        <v>-3.185876721271209</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.8508797878708388</v>
       </c>
       <c r="E96">
-        <v>-33.36004966652676</v>
+        <v>-33.41760486906623</v>
       </c>
       <c r="F96">
-        <v>2.055794856078346</v>
+        <v>2.877389526992562</v>
       </c>
       <c r="G96">
-        <v>-2.742347765665337</v>
+        <v>-2.847923666185368</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.212511624790597</v>
       </c>
       <c r="E97">
-        <v>-35.85403853084666</v>
+        <v>-35.62529834052607</v>
       </c>
       <c r="F97">
-        <v>2.090543211890979</v>
+        <v>2.886622510064166</v>
       </c>
       <c r="G97">
-        <v>-2.911581451550483</v>
+        <v>-3.085989633215215</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.594024312494834</v>
       </c>
       <c r="E98">
-        <v>-38.76253034501843</v>
+        <v>-38.54746460298483</v>
       </c>
       <c r="F98">
-        <v>2.216932196740517</v>
+        <v>2.814327573352242</v>
       </c>
       <c r="G98">
-        <v>-3.029939557588603</v>
+        <v>-3.281469134474822</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.96495967096163</v>
       </c>
       <c r="E99">
-        <v>-40.82409722922549</v>
+        <v>-40.79428755494153</v>
       </c>
       <c r="F99">
-        <v>2.015503065606178</v>
+        <v>2.721687933227562</v>
       </c>
       <c r="G99">
-        <v>-3.116054967926475</v>
+        <v>-3.438823932470402</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.311220583681416</v>
       </c>
       <c r="E100">
-        <v>-43.68476066178053</v>
+        <v>-42.91403677659812</v>
       </c>
       <c r="F100">
-        <v>1.853070158326028</v>
+        <v>2.734560762667066</v>
       </c>
       <c r="G100">
-        <v>-3.584432990550563</v>
+        <v>-3.192356589346352</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.599019942658316</v>
       </c>
       <c r="E101">
-        <v>-46.48443937754462</v>
+        <v>-45.00975136431794</v>
       </c>
       <c r="F101">
-        <v>1.408919437762601</v>
+        <v>2.770614625506512</v>
       </c>
       <c r="G101">
-        <v>-3.011092592385357</v>
+        <v>-3.344855402402461</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.839937363174843</v>
       </c>
       <c r="E102">
-        <v>-48.92985955032915</v>
+        <v>-47.76847422490506</v>
       </c>
       <c r="F102">
-        <v>1.565025274820167</v>
+        <v>2.771956580699047</v>
       </c>
       <c r="G102">
-        <v>-3.680325639382154</v>
+        <v>-3.803153340160261</v>
       </c>
     </row>
   </sheetData>
